--- a/results/Threshold_Selections.xlsx
+++ b/results/Threshold_Selections.xlsx
@@ -425,34 +425,250 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>chosen_threshold_min_fn_bounded_fp</t>
+          <t>objective</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>chosen_threshold_max_mcc_recall_constraint</t>
+          <t>chosen_threshold</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>chosen_threshold_max_balacc_recall_constraint</t>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>recall1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>precision1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fpr</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>mcc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>bal_acc</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>threshold</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>min_fn_bounded_fp</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0.25</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Constraints satisfied.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G2" t="n">
+        <v>161</v>
+      </c>
+      <c r="H2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8297872340425532</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6296296296296297</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1297297297297297</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.5223315824882198</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.7751351351351352</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_mcc_with_recall_constraint</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>0.21</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Constraints satisfied.</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G3" t="n">
+        <v>143</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7574468085106383</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5511811023622047</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.227027027027027</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4124138910773641</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7364864864864864</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>max_bal_acc_with_recall_constraint</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Constraints satisfied.</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>38</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53</v>
+      </c>
+      <c r="G4" t="n">
+        <v>132</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4175824175824176</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.723404255319149</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5390070921985816</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2864864864864865</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3978334554451879</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7367567567567568</v>
+      </c>
+      <c r="P4" t="n">
         <v>0.19</v>
       </c>
     </row>
